--- a/api/2/xlsx/pt/AidType.xlsx
+++ b/api/2/xlsx/pt/AidType.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="61">
   <si>
     <t>code</t>
   </si>
@@ -191,6 +191,12 @@
   </si>
   <si>
     <t>H06</t>
+  </si>
+  <si>
+    <t>J01</t>
+  </si>
+  <si>
+    <t>J</t>
   </si>
 </sst>
 </file>
@@ -522,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -877,6 +883,17 @@
         <v>7</v>
       </c>
     </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
